--- a/media/sns6-checklist.xlsx
+++ b/media/sns6-checklist.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ksajh\claude-app\cacaotalk\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ksajh\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70E0C92B-9C6F-4FF6-80E1-2FF9B37EBFD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F254E29-DA85-4BBF-A4DD-1121B86F3296}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18780" yWindow="-15360" windowWidth="18960" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24120" yWindow="-16200" windowWidth="19725" windowHeight="16305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="참가자 준비표" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="126">
   <si>
     <t>SNS 6종 자동화 과정 — 사전 준비 체크시트</t>
   </si>
@@ -87,9 +87,6 @@
     <t>선택</t>
   </si>
   <si>
-    <t>AIza… (발급 후 기록)</t>
-  </si>
-  <si>
     <t>③ 네이버</t>
   </si>
   <si>
@@ -111,9 +108,6 @@
     <t>권장</t>
   </si>
   <si>
-    <t>완료 / 아직</t>
-  </si>
-  <si>
     <t>④ 티스토리</t>
   </si>
   <si>
@@ -135,9 +129,6 @@
     <t>참고</t>
   </si>
   <si>
-    <t>숫자형 / 문자형</t>
-  </si>
-  <si>
     <t>⑤ 홈페이지</t>
   </si>
   <si>
@@ -147,9 +138,6 @@
     <t>GitHub 계정</t>
   </si>
   <si>
-    <t>hong</t>
-  </si>
-  <si>
     <t>github.com/hong</t>
   </si>
   <si>
@@ -180,18 +168,12 @@
     <t>★ 프로페셔널(비즈니스) 계정 확인</t>
   </si>
   <si>
-    <t>이미 비즈니스 / 전환함 / 아직</t>
-  </si>
-  <si>
     <t>페이스북 계정</t>
   </si>
   <si>
     <t>★ 인스타그램 액세스 토큰</t>
   </si>
   <si>
-    <t>IGAA… (발급 후 기록)</t>
-  </si>
-  <si>
     <t>⑦ 스레드</t>
   </si>
   <si>
@@ -201,18 +183,12 @@
     <t>★ 스레드 액세스 토큰</t>
   </si>
   <si>
-    <t>THQV… (발급 후 기록)</t>
-  </si>
-  <si>
     <t>⑧ 유튜브</t>
   </si>
   <si>
     <t>유튜브 계정</t>
   </si>
   <si>
-    <t>구글 계정과 동일</t>
-  </si>
-  <si>
     <t>본인 채널 주소</t>
   </si>
   <si>
@@ -222,9 +198,6 @@
     <t>2단계 인증 / 업로드 권한</t>
   </si>
   <si>
-    <t>확인함 / 아직</t>
-  </si>
-  <si>
     <t>★ 미리 안 해두면 당일 진도가 막히는 것</t>
   </si>
   <si>
@@ -396,22 +369,55 @@
     <t>미인증 계정은 업로드가 막힌다</t>
   </si>
   <si>
-    <t>hong@gmail.com 또는 010-0000-0000</t>
-  </si>
-  <si>
     <t>클로드 맥스 110</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>맥스 110 여부 / 예 / 아니요</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>블로그에 업로드할 카테고리 이름</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">AIza… </t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>맥스 여부 / 예 / 아니요</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>예) 교육후기</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>깃허브-버셀 개인 홈페이지 운영</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>지메일로 로그인</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>json파일</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>가입 메일</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">    메타(페이스북)으로 부터 오는 인증문자(6자리)가 관건 입니다. 폰에서 차단된 메시지를 꼭 확인하세요.</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>노란색 부분만 미리 준비하세요.</t>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -460,21 +466,6 @@
       <charset val="129"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF909090"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFB0B0B0"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF2B58E0"/>
@@ -504,8 +495,38 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="G마켓 산스 Bold"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -542,8 +563,20 @@
         <fgColor rgb="FFFDEDED"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -566,11 +599,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFB4C6E7"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -584,33 +626,48 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -913,7 +970,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -926,26 +983,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
     </row>
     <row r="2" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+    </row>
+    <row r="3" spans="1:7" ht="46.3" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D3" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="E3" s="22"/>
     </row>
     <row r="4" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
@@ -975,19 +1038,19 @@
         <v>9</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="9"/>
-      <c r="F5" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="G5" s="8"/>
+      <c r="D5" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="E5" s="14"/>
+      <c r="F5" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="G5" s="5"/>
     </row>
     <row r="6" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="2" t="s">
@@ -999,401 +1062,371 @@
       <c r="C6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="9"/>
-      <c r="F6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" s="8"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="5"/>
     </row>
     <row r="7" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="2"/>
       <c r="B7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G7" s="8"/>
+      <c r="D7" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="G7" s="5"/>
     </row>
     <row r="8" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="9"/>
-      <c r="F8" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8" s="8"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="5"/>
     </row>
     <row r="9" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="2"/>
       <c r="B9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G9" s="8"/>
+      <c r="G9" s="5"/>
     </row>
     <row r="10" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="2"/>
       <c r="B10" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="G10" s="8"/>
+      <c r="D10" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="G10" s="5"/>
     </row>
     <row r="11" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E11" s="9"/>
-      <c r="F11" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11" s="8"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11" s="5"/>
     </row>
     <row r="12" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="2"/>
       <c r="B12" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G12" s="8"/>
+      <c r="D12" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" s="5"/>
     </row>
     <row r="13" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="2"/>
+      <c r="A13" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="B13" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" s="5"/>
+    </row>
+    <row r="14" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="2"/>
+      <c r="B14" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="G13" s="8"/>
-    </row>
-    <row r="14" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="2" t="s">
+      <c r="C14" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="E14" s="14"/>
+      <c r="F14" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14" s="8"/>
+      <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="2"/>
       <c r="B15" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E15" s="9"/>
-      <c r="F15" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G15" s="8"/>
+      <c r="G15" s="5"/>
     </row>
     <row r="16" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="2"/>
       <c r="B16" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="C16" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" s="7" t="s">
+      <c r="G16" s="5"/>
+    </row>
+    <row r="17" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="G16" s="8"/>
-    </row>
-    <row r="17" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="2"/>
       <c r="B17" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D17" s="7" t="s">
+      <c r="C17" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="E17" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F17" s="7" t="s">
+      <c r="E17" s="14"/>
+      <c r="F17" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17" s="5"/>
+    </row>
+    <row r="18" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="2"/>
+      <c r="B18" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="G17" s="8"/>
-    </row>
-    <row r="18" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="C18" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D18" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E18" s="9"/>
-      <c r="F18" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G18" s="8"/>
+      <c r="D18" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="18"/>
+      <c r="G18" s="5"/>
     </row>
     <row r="19" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="2"/>
-      <c r="B19" s="11" t="s">
-        <v>51</v>
+      <c r="B19" s="3" t="s">
+        <v>48</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D19" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="G19" s="8"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="G19" s="5"/>
     </row>
     <row r="20" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="2"/>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" s="20"/>
+      <c r="G20" s="5"/>
+    </row>
+    <row r="21" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D21" s="18"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="G21" s="5"/>
+    </row>
+    <row r="22" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="2"/>
+      <c r="B22" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="20"/>
+      <c r="G22" s="5"/>
+    </row>
+    <row r="23" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C20" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="E20" s="9"/>
-      <c r="F20" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G20" s="8"/>
-    </row>
-    <row r="21" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="2"/>
-      <c r="B21" s="11" t="s">
+      <c r="B23" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C21" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F21" s="7" t="s">
+      <c r="C23" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="18"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="G23" s="5"/>
+    </row>
+    <row r="24" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="2"/>
+      <c r="B24" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="G21" s="8"/>
-    </row>
-    <row r="22" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="2" t="s">
+      <c r="C24" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D24" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E22" s="9"/>
-      <c r="F22" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G22" s="8"/>
-    </row>
-    <row r="23" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="2"/>
-      <c r="B23" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="G23" s="8"/>
-    </row>
-    <row r="24" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="E24" s="9"/>
-      <c r="F24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G24" s="8"/>
+      <c r="G24" s="5"/>
     </row>
     <row r="25" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="2"/>
       <c r="B25" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C25" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C25" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G25" s="8"/>
-    </row>
-    <row r="26" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="2"/>
-      <c r="B26" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C26" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="G26" s="8"/>
+      <c r="D25" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="G25" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="D3:E3"/>
   </mergeCells>
-  <phoneticPr fontId="11" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="G5:G26" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="G5:G25" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"O,X"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1403,169 +1436,174 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:A43"/>
+  <dimension ref="A1:A44"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="96" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="19.75" x14ac:dyDescent="0.6">
-      <c r="A1" s="12" t="s">
-        <v>67</v>
+      <c r="A1" s="8" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="13" t="s">
-        <v>68</v>
+      <c r="A3" s="9" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="13" t="s">
-        <v>73</v>
+      <c r="A9" s="9" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="13" t="s">
-        <v>76</v>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" t="s">
-        <v>77</v>
+      <c r="A14" s="9" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="13" t="s">
-        <v>79</v>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" t="s">
-        <v>80</v>
+      <c r="A18" s="9" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="13" t="s">
-        <v>83</v>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="13" t="s">
-        <v>85</v>
+      <c r="A23" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" ht="19.75" x14ac:dyDescent="0.6">
-      <c r="A29" s="12" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="13" t="s">
-        <v>88</v>
+      <c r="A26" s="9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" ht="19.75" x14ac:dyDescent="0.6">
+      <c r="A30" s="8" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="13" t="s">
-        <v>89</v>
+      <c r="A32" s="9" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="13" t="s">
-        <v>90</v>
+      <c r="A33" s="9" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" t="s">
-        <v>91</v>
+      <c r="A34" s="9" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" ht="19.75" x14ac:dyDescent="0.6">
-      <c r="A39" s="12" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="13" t="s">
-        <v>95</v>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" ht="19.75" x14ac:dyDescent="0.6">
+      <c r="A40" s="8" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="13" t="s">
-        <v>96</v>
+      <c r="A42" s="9" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="13" t="s">
-        <v>97</v>
+      <c r="A43" s="9" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" s="9" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="11" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1582,371 +1620,371 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" s="14" t="s">
+      <c r="C1" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="3" t="s">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="s">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="3" t="s">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5" s="3" t="s">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D6" s="3" t="s">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="8" t="s">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" s="3" t="s">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D9" s="3" t="s">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="3" t="s">
+    <row r="19" spans="1:4" ht="35.15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D11" s="3" t="s">
+    <row r="20" spans="1:4" ht="35.15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D12" s="3" t="s">
+    <row r="21" spans="1:4" ht="35.15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D13" s="3" t="s">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C14" s="8" t="s">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C24" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C15" s="8" t="s">
+      <c r="D24" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C25" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C16" s="8" t="s">
+      <c r="D25" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C26" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D17" s="3" t="s">
+      <c r="D26" s="3" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="35.15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="35.15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="35.15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>123</v>
-      </c>
-    </row>
   </sheetData>
-  <phoneticPr fontId="11" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>